--- a/gym_membership_tracker_template.xlsx
+++ b/gym_membership_tracker_template.xlsx
@@ -269,7 +269,7 @@
     <numFmt numFmtId="167" formatCode="General"/>
     <numFmt numFmtId="168" formatCode="0"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -347,16 +347,32 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="9"/>
+      <sz val="13"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
+      <i val="true"/>
+      <sz val="12"/>
+      <color rgb="FFC9DFC2"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
-      <sz val="14"/>
-      <color rgb="FF2F5233"/>
+      <sz val="9"/>
+      <color rgb="FF1F3B21"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="16"/>
+      <color rgb="FF1F3B21"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -382,7 +398,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -392,7 +408,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2F5233"/>
-        <bgColor rgb="FF555555"/>
+        <bgColor rgb="FF1F3B21"/>
       </patternFill>
     </fill>
     <fill>
@@ -403,18 +419,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4C7A47"/>
-        <bgColor rgb="FF555555"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFF5EC"/>
-        <bgColor rgb="FFFDEEEE"/>
+        <fgColor rgb="FFDCEAD5"/>
+        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -434,6 +444,52 @@
       </top>
       <bottom style="thin">
         <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FF4C7A47"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF4C7A47"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF4C7A47"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF4C7A47"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF4C7A47"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin">
+        <color rgb="FF4C7A47"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF4C7A47"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF4C7A47"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF2F5233"/>
       </bottom>
       <diagonal/>
     </border>
@@ -463,7 +519,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -520,20 +576,44 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -590,7 +670,7 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FFC0504D"/>
       <rgbColor rgb="FFFFFDE7"/>
-      <rgbColor rgb="FFEFF5EC"/>
+      <rgbColor rgb="FFFDEEEE"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -604,8 +684,8 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFFDEEEE"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFC9DFC2"/>
+      <rgbColor rgb="FFDCEAD5"/>
       <rgbColor rgb="FFFDEBD0"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -622,11 +702,11 @@
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF4C7A47"/>
       <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF2F5233"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF555555"/>
-      <rgbColor rgb="FF2F5233"/>
+      <rgbColor rgb="FF1F3B21"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -760,12 +840,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="1"/>
@@ -784,12 +865,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="2"/>
@@ -808,12 +890,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="3"/>
@@ -832,12 +915,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="4"/>
@@ -856,12 +940,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:txPr>
               <a:bodyPr wrap="square"/>
@@ -878,12 +963,13 @@
               </a:p>
             </c:txPr>
             <c:dLblPos val="bestFit"/>
-            <c:showLegendKey val="1"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="1"/>
-            <c:showSerName val="1"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
             <c:showPercent val="1"/>
-            <c:separator>; </c:separator>
+            <c:separator>
+</c:separator>
             <c:showLeaderLines val="1"/>
           </c:dLbls>
           <c:cat>
@@ -1045,10 +1131,12 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4f81bd"/>
+              <a:srgbClr val="2f5233"/>
             </a:solidFill>
             <a:ln w="0">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="2f5233"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="0"/>
@@ -1169,11 +1257,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="17922267"/>
-        <c:axId val="30430718"/>
+        <c:axId val="66017222"/>
+        <c:axId val="40972019"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="17922267"/>
+        <c:axId val="66017222"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1205,7 +1293,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30430718"/>
+        <c:crossAx val="40972019"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1213,7 +1301,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="30430718"/>
+        <c:axId val="40972019"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1289,7 +1377,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17922267"/>
+        <c:crossAx val="66017222"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1347,14 +1435,14 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>481680</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>18000</xdr:rowOff>
+      <xdr:rowOff>32400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1362,7 +1450,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4444920" y="1828800"/>
+        <a:off x="4444920" y="2104920"/>
         <a:ext cx="3599640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -1377,14 +1465,14 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>365400</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>18000</xdr:rowOff>
+      <xdr:rowOff>32760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1392,7 +1480,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4444920" y="3924360"/>
+        <a:off x="4444920" y="4200480"/>
         <a:ext cx="5759640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -6505,75 +6593,83 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+    </row>
+    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="14" t="n">
+      <c r="B3" s="16" t="n">
         <v>2026</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="14" t="n">
+      <c r="D3" s="18" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="15" t="s">
+    <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="19" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="n">
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+    </row>
+    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="n">
         <f aca="false">COUNTIF(Members!$G$3:$G$102,"Active")</f>
         <v>0</v>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="22" t="n">
         <f aca="false">SUMIFS(Payments!$C$3:$C$152,Payments!$E$3:$E$152,$B$3,Payments!$F$3:$F$152,$D$3)</f>
         <v>0</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="22" t="n">
         <f aca="false">IFERROR(B6/A6,0)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="21" t="n">
         <f aca="false">COUNTIFS(Members!$G$3:$G$102,"Active",Members!$I$3:$I$102,"&gt;=0",Members!$I$3:$I$102,"&lt;=7")</f>
         <v>0</v>
       </c>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
@@ -6581,10 +6677,10 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="23" t="s">
         <v>47</v>
       </c>
     </row>
@@ -6639,10 +6735,10 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="23" t="s">
         <v>49</v>
       </c>
     </row>
@@ -6650,7 +6746,7 @@
       <c r="A22" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B22" s="18" t="n">
+      <c r="B22" s="24" t="n">
         <f aca="false">SUMIFS(Payments!$C$3:$C$152,Payments!$E$3:$E$152,$B$3,Payments!$F$3:$F$152,1)</f>
         <v>0</v>
       </c>
@@ -6659,7 +6755,7 @@
       <c r="A23" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="18" t="n">
+      <c r="B23" s="24" t="n">
         <f aca="false">SUMIFS(Payments!$C$3:$C$152,Payments!$E$3:$E$152,$B$3,Payments!$F$3:$F$152,2)</f>
         <v>0</v>
       </c>
@@ -6668,7 +6764,7 @@
       <c r="A24" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="18" t="n">
+      <c r="B24" s="24" t="n">
         <f aca="false">SUMIFS(Payments!$C$3:$C$152,Payments!$E$3:$E$152,$B$3,Payments!$F$3:$F$152,3)</f>
         <v>0</v>
       </c>
@@ -6677,7 +6773,7 @@
       <c r="A25" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B25" s="18" t="n">
+      <c r="B25" s="24" t="n">
         <f aca="false">SUMIFS(Payments!$C$3:$C$152,Payments!$E$3:$E$152,$B$3,Payments!$F$3:$F$152,4)</f>
         <v>0</v>
       </c>
@@ -6686,7 +6782,7 @@
       <c r="A26" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B26" s="18" t="n">
+      <c r="B26" s="24" t="n">
         <f aca="false">SUMIFS(Payments!$C$3:$C$152,Payments!$E$3:$E$152,$B$3,Payments!$F$3:$F$152,5)</f>
         <v>0</v>
       </c>
@@ -6695,7 +6791,7 @@
       <c r="A27" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B27" s="18" t="n">
+      <c r="B27" s="24" t="n">
         <f aca="false">SUMIFS(Payments!$C$3:$C$152,Payments!$E$3:$E$152,$B$3,Payments!$F$3:$F$152,6)</f>
         <v>0</v>
       </c>
@@ -6704,7 +6800,7 @@
       <c r="A28" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="18" t="n">
+      <c r="B28" s="24" t="n">
         <f aca="false">SUMIFS(Payments!$C$3:$C$152,Payments!$E$3:$E$152,$B$3,Payments!$F$3:$F$152,7)</f>
         <v>0</v>
       </c>
@@ -6713,7 +6809,7 @@
       <c r="A29" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B29" s="18" t="n">
+      <c r="B29" s="24" t="n">
         <f aca="false">SUMIFS(Payments!$C$3:$C$152,Payments!$E$3:$E$152,$B$3,Payments!$F$3:$F$152,8)</f>
         <v>0</v>
       </c>
@@ -6722,7 +6818,7 @@
       <c r="A30" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="18" t="n">
+      <c r="B30" s="24" t="n">
         <f aca="false">SUMIFS(Payments!$C$3:$C$152,Payments!$E$3:$E$152,$B$3,Payments!$F$3:$F$152,9)</f>
         <v>0</v>
       </c>
@@ -6731,7 +6827,7 @@
       <c r="A31" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B31" s="18" t="n">
+      <c r="B31" s="24" t="n">
         <f aca="false">SUMIFS(Payments!$C$3:$C$152,Payments!$E$3:$E$152,$B$3,Payments!$F$3:$F$152,10)</f>
         <v>0</v>
       </c>
@@ -6740,7 +6836,7 @@
       <c r="A32" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B32" s="18" t="n">
+      <c r="B32" s="24" t="n">
         <f aca="false">SUMIFS(Payments!$C$3:$C$152,Payments!$E$3:$E$152,$B$3,Payments!$F$3:$F$152,11)</f>
         <v>0</v>
       </c>
@@ -6749,7 +6845,7 @@
       <c r="A33" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B33" s="18" t="n">
+      <c r="B33" s="24" t="n">
         <f aca="false">SUMIFS(Payments!$C$3:$C$152,Payments!$E$3:$E$152,$B$3,Payments!$F$3:$F$152,12)</f>
         <v>0</v>
       </c>
@@ -6812,7 +6908,7 @@
       <c r="A4" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="25" t="s">
         <v>66</v>
       </c>
     </row>
@@ -6820,7 +6916,7 @@
       <c r="A5" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="25" t="s">
         <v>68</v>
       </c>
     </row>
@@ -6828,7 +6924,7 @@
       <c r="A6" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="25" t="s">
         <v>70</v>
       </c>
     </row>
@@ -6836,7 +6932,7 @@
       <c r="A7" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="25" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6844,7 +6940,7 @@
       <c r="A8" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="25" t="s">
         <v>74</v>
       </c>
     </row>
@@ -6852,7 +6948,7 @@
       <c r="A9" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="25" t="s">
         <v>76</v>
       </c>
     </row>
